--- a/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos</t>
+          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 14,95</t>
+          <t>12,47; 15,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,25</t>
+          <t>9,06; 14,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 18,29</t>
+          <t>11,91; 17,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 16,5</t>
+          <t>8,33; 16,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,0; 21,77</t>
+          <t>14,92; 21,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 15,38</t>
+          <t>10,53; 15,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 17,48</t>
+          <t>11,34; 17,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,17</t>
+          <t>8,03; 13,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 17,75</t>
+          <t>14,07; 18,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 13,78</t>
+          <t>10,36; 14,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,56</t>
+          <t>12,31; 16,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,5</t>
+          <t>8,94; 13,83</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 15,72</t>
+          <t>12,7; 15,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 13,39</t>
+          <t>10,23; 13,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 11,26</t>
+          <t>9,4; 11,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 20,67</t>
+          <t>9,45; 20,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,2</t>
+          <t>11,94; 15,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,29</t>
+          <t>9,95; 12,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 11,82</t>
+          <t>9,15; 11,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,26</t>
+          <t>8,16; 17,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 14,75</t>
+          <t>12,49; 14,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,64</t>
+          <t>10,35; 12,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,05</t>
+          <t>9,57; 11,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 16,68</t>
+          <t>9,92; 16,88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 16,78</t>
+          <t>13,84; 16,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 15,95</t>
+          <t>11,94; 15,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 15,51</t>
+          <t>10,89; 15,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,75</t>
+          <t>10,08; 15,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,25</t>
+          <t>14,08; 16,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 13,91</t>
+          <t>10,99; 13,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,38</t>
+          <t>9,7; 12,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 15,94</t>
+          <t>10,38; 16,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 16,04</t>
+          <t>14,4; 16,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 14,39</t>
+          <t>11,76; 14,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 13,23</t>
+          <t>10,55; 13,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 14,77</t>
+          <t>10,76; 14,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 17,8</t>
+          <t>14,07; 18,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,85</t>
+          <t>9,34; 13,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,34</t>
+          <t>9,15; 12,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,33; 18,5</t>
+          <t>10,19; 19,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,1</t>
+          <t>12,3; 15,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,59</t>
+          <t>8,85; 13,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,66</t>
+          <t>11,02; 15,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,38</t>
+          <t>9,95; 15,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,93</t>
+          <t>13,47; 16,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,03</t>
+          <t>9,61; 12,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,21</t>
+          <t>10,5; 13,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 16,16</t>
+          <t>10,89; 16,14</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,33</t>
+          <t>11,78; 16,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,27</t>
+          <t>8,25; 12,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,06</t>
+          <t>10,12; 14,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 16,63</t>
+          <t>11,92; 16,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,98</t>
+          <t>11,52; 15,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 10,63</t>
+          <t>8,17; 10,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,6</t>
+          <t>9,17; 11,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 17,76</t>
+          <t>12,08; 17,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 15,16</t>
+          <t>12,21; 15,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,79</t>
+          <t>8,59; 10,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 12,12</t>
+          <t>10,01; 12,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,45</t>
+          <t>12,72; 16,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 16,44</t>
+          <t>12,68; 16,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,39; 14,71</t>
+          <t>10,27; 14,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,02</t>
+          <t>10,56; 12,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 14,01</t>
+          <t>7,2; 13,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,91; 15,84</t>
+          <t>11,93; 15,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,72</t>
+          <t>10,89; 14,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,95</t>
+          <t>10,83; 13,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,1</t>
+          <t>8,93; 15,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,67; 15,17</t>
+          <t>12,7; 15,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,85; 13,84</t>
+          <t>11,0; 13,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,93; 12,82</t>
+          <t>10,98; 12,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,51</t>
+          <t>9,01; 13,6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 13,7</t>
+          <t>11,92; 13,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,63</t>
+          <t>12,38; 14,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 12,95</t>
+          <t>10,97; 13,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,13; 21,51</t>
+          <t>10,25; 21,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 14,33</t>
+          <t>12,26; 14,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 13,99</t>
+          <t>11,87; 13,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,36</t>
+          <t>11,68; 14,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,01; 20,31</t>
+          <t>10,75; 21,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 13,67</t>
+          <t>12,33; 13,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,41; 13,88</t>
+          <t>12,39; 13,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,6; 13,26</t>
+          <t>11,75; 13,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,9</t>
+          <t>11,46; 19,03</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,63</t>
+          <t>13,24; 15,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 12,9</t>
+          <t>10,98; 12,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,44; 11,86</t>
+          <t>10,51; 11,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 40,64</t>
+          <t>10,59; 40,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,92</t>
+          <t>12,72; 14,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,62</t>
+          <t>11,48; 13,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,96; 12,6</t>
+          <t>10,93; 12,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,08; 18,04</t>
+          <t>11,0; 17,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 14,86</t>
+          <t>13,24; 14,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,89</t>
+          <t>11,45; 12,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,97</t>
+          <t>10,91; 11,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,73; 21,5</t>
+          <t>11,91; 23,44</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,59</t>
+          <t>13,59; 14,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,65</t>
+          <t>11,47; 12,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,07</t>
+          <t>11,08; 12,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,8</t>
+          <t>11,82; 16,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,45; 14,51</t>
+          <t>13,41; 14,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,5</t>
+          <t>11,39; 12,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,45</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,51; 14,38</t>
+          <t>11,45; 14,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,37</t>
+          <t>13,63; 14,42</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,38</t>
+          <t>11,59; 12,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,11</t>
+          <t>11,34; 12,09</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,08; 14,49</t>
+          <t>12,16; 14,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,02</t>
+          <t>12,51; 15,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 14,61</t>
+          <t>9,12; 14,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 17,96</t>
+          <t>12,11; 18,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 16,25</t>
+          <t>7,87; 16,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,92; 21,32</t>
+          <t>15,05; 21,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,74</t>
+          <t>10,51; 15,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,17</t>
+          <t>11,35; 17,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,23</t>
+          <t>7,59; 12,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 18,13</t>
+          <t>14,07; 17,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,01</t>
+          <t>10,31; 13,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 16,71</t>
+          <t>12,28; 16,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,83</t>
+          <t>8,93; 13,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 15,85</t>
+          <t>12,62; 15,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 13,36</t>
+          <t>10,24; 13,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,37</t>
+          <t>9,44; 11,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,79</t>
+          <t>9,51; 21,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 15,19</t>
+          <t>11,86; 15,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 12,98</t>
+          <t>9,87; 12,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 11,86</t>
+          <t>9,08; 11,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,22</t>
+          <t>8,72; 17,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 14,69</t>
+          <t>12,6; 14,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,47</t>
+          <t>10,34; 12,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 11,24</t>
+          <t>9,52; 11,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,88</t>
+          <t>10,25; 16,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 16,51</t>
+          <t>13,96; 16,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 15,93</t>
+          <t>11,86; 16,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,8</t>
+          <t>10,89; 15,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,73</t>
+          <t>10,19; 15,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 16,48</t>
+          <t>14,13; 16,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,97</t>
+          <t>10,99; 13,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 12,64</t>
+          <t>9,65; 12,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,35</t>
+          <t>10,64; 16,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,1</t>
+          <t>14,35; 16,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,14</t>
+          <t>11,85; 14,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,45</t>
+          <t>10,51; 13,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,62</t>
+          <t>10,89; 14,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 18,36</t>
+          <t>14,03; 18,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,89</t>
+          <t>9,5; 13,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,21</t>
+          <t>9,09; 12,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,64</t>
+          <t>9,13; 19,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,08</t>
+          <t>12,34; 14,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,62</t>
+          <t>9,06; 13,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 15,45</t>
+          <t>10,87; 15,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,69</t>
+          <t>9,98; 16,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,06</t>
+          <t>13,63; 16,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,86</t>
+          <t>9,66; 12,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,14</t>
+          <t>10,4; 13,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,14</t>
+          <t>10,93; 16,42</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 16,26</t>
+          <t>11,87; 16,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,37</t>
+          <t>8,41; 12,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,33</t>
+          <t>10,25; 14,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,42 +1296,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,46</t>
+          <t>11,46; 15,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 10,73</t>
+          <t>8,19; 10,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 11,53</t>
+          <t>9,12; 11,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,73</t>
+          <t>12,1; 17,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,25</t>
+          <t>12,06; 15,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,82</t>
+          <t>8,52; 10,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,21</t>
+          <t>9,9; 12,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,72; 16,54</t>
+          <t>12,73; 16,42</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,68; 16,0</t>
+          <t>12,77; 16,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,49</t>
+          <t>10,26; 14,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,89</t>
+          <t>10,59; 12,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 13,6</t>
+          <t>6,9; 13,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,93; 15,63</t>
+          <t>11,92; 15,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,8</t>
+          <t>10,71; 14,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 13,98</t>
+          <t>10,81; 13,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 15,27</t>
+          <t>9,2; 14,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 15,47</t>
+          <t>12,65; 15,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,74</t>
+          <t>10,98; 13,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 12,88</t>
+          <t>11,07; 12,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,6</t>
+          <t>9,21; 13,85</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,92; 13,59</t>
+          <t>11,94; 13,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 14,64</t>
+          <t>12,35; 14,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,13</t>
+          <t>10,85; 13,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 21,97</t>
+          <t>10,07; 21,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,22</t>
+          <t>12,27; 14,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 13,95</t>
+          <t>11,87; 13,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,68; 14,2</t>
+          <t>11,75; 14,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 21,39</t>
+          <t>10,69; 20,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 13,66</t>
+          <t>12,36; 13,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 13,98</t>
+          <t>12,4; 13,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 13,31</t>
+          <t>11,6; 13,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 19,03</t>
+          <t>11,66; 19,0</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,24; 15,61</t>
+          <t>13,26; 15,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,98; 12,87</t>
+          <t>10,9; 12,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,51; 11,89</t>
+          <t>10,46; 11,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,59; 40,43</t>
+          <t>10,66; 38,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,72; 14,84</t>
+          <t>12,7; 14,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,48; 13,38</t>
+          <t>11,49; 13,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 12,5</t>
+          <t>10,88; 12,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,47</t>
+          <t>11,08; 17,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,24; 14,89</t>
+          <t>13,25; 14,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,45; 12,91</t>
+          <t>11,41; 12,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 11,95</t>
+          <t>10,87; 11,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 23,44</t>
+          <t>11,91; 22,57</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,57</t>
+          <t>13,58; 14,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,63</t>
+          <t>11,47; 12,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,05</t>
+          <t>11,07; 12,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,51</t>
+          <t>12,02; 16,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,41; 14,53</t>
+          <t>13,46; 14,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,49</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,29; 12,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,27</t>
+          <t>11,61; 14,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,42</t>
+          <t>13,67; 14,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,37</t>
+          <t>11,58; 12,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,09</t>
+          <t>11,36; 12,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,55</t>
+          <t>12,12; 14,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Provincia-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
+          <t>Tiempo medio en minutos que dura el trayecto desde su domicilio a la consulta médica (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,65</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,33</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,46</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 15,09</t>
+          <t>15,0; 21,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,49</t>
+          <t>10,54; 15,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 18,16</t>
+          <t>11,61; 17,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 16,17</t>
+          <t>7,81; 13,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 21,68</t>
+          <t>12,45; 14,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,54</t>
+          <t>9,16; 14,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 17,22</t>
+          <t>11,86; 18,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,93</t>
+          <t>8,33; 16,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 17,53</t>
+          <t>14,12; 17,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 13,89</t>
+          <t>10,33; 13,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,49</t>
+          <t>12,22; 16,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,48</t>
+          <t>9,06; 13,59</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,08</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,04</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,28</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,32</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>13,87</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,38</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,29</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,08</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,04</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13,97</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13,46</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11,21</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>10,28</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,07</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13,46</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10,28</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>13,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 15,58</t>
+          <t>11,8; 15,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 13,63</t>
+          <t>9,9; 13,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 11,41</t>
+          <t>9,06; 11,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 21,35</t>
+          <t>8,39; 17,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,43</t>
+          <t>12,61; 15,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 12,96</t>
+          <t>10,2; 13,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,77</t>
+          <t>9,32; 11,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 17,53</t>
+          <t>9,31; 21,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 14,66</t>
+          <t>12,56; 14,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,5</t>
+          <t>10,34; 12,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,14</t>
+          <t>9,51; 11,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 16,92</t>
+          <t>10,1; 17,5</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,08</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15,19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12,35</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,4</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,12</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,2</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,6</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>12,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 16,59</t>
+          <t>14,06; 16,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,86; 16,12</t>
+          <t>11,1; 13,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,9</t>
+          <t>9,61; 12,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,92</t>
+          <t>10,3; 16,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 16,45</t>
+          <t>13,97; 16,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,9</t>
+          <t>11,87; 15,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 12,5</t>
+          <t>10,81; 15,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,35</t>
+          <t>10,27; 16,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,04</t>
+          <t>14,34; 16,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,31</t>
+          <t>11,8; 14,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 13,16</t>
+          <t>10,57; 13,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,88</t>
+          <t>11,01; 14,9</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,72</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,76</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,59</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,72</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,76</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,08</t>
+          <t>12,43; 15,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,82</t>
+          <t>8,93; 13,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,19</t>
+          <t>10,94; 15,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 19,01</t>
+          <t>9,58; 15,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 14,99</t>
+          <t>13,99; 17,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,85</t>
+          <t>9,35; 13,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 15,36</t>
+          <t>9,17; 12,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 16,02</t>
+          <t>9,65; 22,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,12</t>
+          <t>13,52; 15,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,77</t>
+          <t>9,65; 13,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 13,2</t>
+          <t>10,44; 13,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,42</t>
+          <t>10,93; 17,55</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10,1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14,66</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,66</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,78</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,23</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,34</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,1</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,65</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,48</t>
+          <t>14,47</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 16,36</t>
+          <t>11,67; 15,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,06</t>
+          <t>8,2; 10,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,08</t>
+          <t>9,14; 11,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,59</t>
+          <t>11,68; 17,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,56</t>
+          <t>11,64; 16,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 10,76</t>
+          <t>8,35; 12,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,56</t>
+          <t>10,21; 14,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,92</t>
+          <t>12,08; 16,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 15,15</t>
+          <t>12,16; 15,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 10,83</t>
+          <t>8,51; 10,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 12,28</t>
+          <t>9,94; 12,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 16,42</t>
+          <t>12,58; 16,45</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13,37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12,08</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11,85</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>14,06</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12,04</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11,7</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10,22</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,37</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,3</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,08</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>11,33</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 16,55</t>
+          <t>11,91; 15,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,34</t>
+          <t>10,86; 14,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,59; 12,93</t>
+          <t>10,6; 13,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,31</t>
+          <t>8,93; 16,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,92; 15,85</t>
+          <t>12,76; 16,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,94</t>
+          <t>10,39; 14,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,81; 13,87</t>
+          <t>10,5; 13,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,72</t>
+          <t>7,34; 14,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 15,11</t>
+          <t>12,67; 15,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,87</t>
+          <t>10,85; 13,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,84</t>
+          <t>10,93; 12,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,85</t>
+          <t>9,15; 14,0</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14,27</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13,47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11,93</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,85</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,79</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,94</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,42</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 13,71</t>
+          <t>12,27; 14,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,35; 14,66</t>
+          <t>11,87; 13,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 13,07</t>
+          <t>11,75; 14,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,07; 21,64</t>
+          <t>11,06; 20,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 14,33</t>
+          <t>11,89; 13,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 13,96</t>
+          <t>12,41; 14,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,42</t>
+          <t>10,79; 12,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 20,48</t>
+          <t>9,57; 22,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 13,64</t>
+          <t>12,36; 13,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,4; 13,95</t>
+          <t>12,41; 13,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,6; 13,3</t>
+          <t>11,6; 13,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,0</t>
+          <t>11,34; 19,23</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,73</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12,36</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,68</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13,93</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>14,32</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>11,79</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>11,12</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16,65</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>13,73</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,68</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>16,19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,77</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,71</t>
+          <t>12,78; 14,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,9; 12,91</t>
+          <t>11,5; 13,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,88</t>
+          <t>10,96; 12,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 38,22</t>
+          <t>11,33; 18,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,7; 14,82</t>
+          <t>13,28; 15,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,49; 13,54</t>
+          <t>10,91; 12,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88; 12,55</t>
+          <t>10,44; 11,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,08; 17,6</t>
+          <t>10,6; 39,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 14,86</t>
+          <t>13,31; 14,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,41; 12,82</t>
+          <t>11,47; 12,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,96</t>
+          <t>10,87; 11,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 22,57</t>
+          <t>11,85; 20,64</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13,92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11,9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11,85</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>14,04</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>12,02</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11,53</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13,92</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,31</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,57</t>
+          <t>13,45; 14,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,6</t>
+          <t>11,37; 12,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,07</t>
+          <t>11,33; 12,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,59</t>
+          <t>11,65; 14,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,46; 14,6</t>
+          <t>13,53; 14,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,47; 12,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,47</t>
+          <t>11,08; 12,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,21</t>
+          <t>11,96; 16,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,67; 14,39</t>
+          <t>13,63; 14,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,58; 12,35</t>
+          <t>11,59; 12,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,36; 12,1</t>
+          <t>11,32; 12,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,64</t>
+          <t>12,14; 14,83</t>
         </is>
       </c>
     </row>
